--- a/history/hi-aitihasik-rajvansh_HI.xlsx
+++ b/history/hi-aitihasik-rajvansh_HI.xlsx
@@ -11,237 +11,690 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="228" uniqueCount="228">
   <si>
     <t>नाम</t>
   </si>
   <si>
-    <t>अंग्रेज़ी नाम</t>
-  </si>
-  <si>
-    <t>स्रोत का अंग्रेज़ी विवरण</t>
-  </si>
-  <si>
-    <t>स्रोत में दर्ज राजधानियाँ</t>
-  </si>
-  <si>
-    <t>वर्गीकरण</t>
+    <t>मूल विवरण</t>
   </si>
   <si>
     <t>स्रोत लिंक</t>
   </si>
   <si>
+    <t>अय राजवंश</t>
+  </si>
+  <si>
+    <t>अय राजवंश एक भारतीय राजवंश था जिसने प्रायद्वीप के दक्षिण-पश्चिमी सिरे को प्रारंभिक ऐतिहासिक काल से मध्यकाल तक नियंत्रित किया था। कबीले ने परंपरागत रूप से विझिंजम के बंदरगाह, नानजिनाद के उपजाऊ क्षेत्र और मसाला-उत्पादक पश्चिमी घाट पहाड़ों के दक्षिणी भागों पर शासन किया। मध्ययुगीन काल में राजवंश को कुपका के नाम से भी जाना जाता था।</t>
+  </si>
+  <si>
+    <t>https://hi.wikipedia.org/w/index.php?title=%E0%A4%85%E0%A4%AF_%E0%A4%B0%E0%A4%BE%E0%A4%9C%E0%A4%B5%E0%A4%82%E0%A4%B6&amp;oldid=5933438</t>
+  </si>
+  <si>
+    <t>अराविदु राजवंश</t>
+  </si>
+  <si>
+    <t>अराविदु राजवंश हिन्दू धर्म का अंतिम राजवंश था जिन्होंने दक्षिण भारत के विजयनगर पर राज किया था। इस राजवंश स्थापक त्रिमूल देव राय थे ,जो कि राम राय के भाई थे। राम राय जो कि पिछले राजवंश के अंतिम शासक थे। इनकी मृत्यु राक्षसी तांगड़ी में हुई थी। अराविदु राजवंश के परिवार के लोग अपना उपनाम अत्रेया रखते थे।</t>
+  </si>
+  <si>
+    <t>https://hi.wikipedia.org/w/index.php?title=%E0%A4%85%E0%A4%B0%E0%A4%BE%E0%A4%B5%E0%A4%BF%E0%A4%A6%E0%A5%81_%E0%A4%B0%E0%A4%BE%E0%A4%9C%E0%A4%B5%E0%A4%82%E0%A4%B6&amp;oldid=6452490</t>
+  </si>
+  <si>
+    <t>आसफ़ जाही राजवंश</t>
+  </si>
+  <si>
+    <t>आसफ जाही एक मुस्लिम राजवंश था जिसने हैदराबाद राज्य पर शासन किया था। राजवंश की स्थापना मीर कमर-उद-दीन सिद्दीकी, दक्कन के एक वायसराय- (छह मुगल शासन के प्रशासक) ने 1713 से 1721 तक मुगल सम्राटों के अधीन की थी। उन्होंने 1707 में औरंगज़ेब की मृत्यु के बाद और आसफ जाह शीर्षक के तहत रुक-रुक कर शासन किया। 1724. मुगल साम्राज्य का पतन हुआ और दक्कन के वायसराय, आसफ जाह I ने खुद को स्वतंत्र घोषित कर दिया, जिसका क्षेत्र उत्तर में नर्मदा नदी से लेकर दक्षिण में त्रिचिनोपोली और पूर्व में मसूलीपट्टनम तक पश्चिम में बीजापुर तक फैला हुआ है।</t>
+  </si>
+  <si>
+    <t>https://hi.wikipedia.org/w/index.php?title=%E0%A4%86%E0%A4%B8%E0%A4%AB%E0%A4%BC_%E0%A4%9C%E0%A4%BE%E0%A4%B9%E0%A5%80_%E0%A4%B0%E0%A4%BE%E0%A4%9C%E0%A4%B5%E0%A4%82%E0%A4%B6&amp;oldid=6569135</t>
+  </si>
+  <si>
+    <t>आहोम राजवंश</t>
+  </si>
+  <si>
+    <t>आहोम वंश‍ (१२२८-१८२६) ने वर्तमान असम के कुछ भागों पर प्रायः ६०० वर्षों तक राज्य किया।</t>
+  </si>
+  <si>
+    <t>https://hi.wikipedia.org/w/index.php?title=%E0%A4%86%E0%A4%B9%E0%A5%8B%E0%A4%AE_%E0%A4%B0%E0%A4%BE%E0%A4%9C%E0%A4%B5%E0%A4%82%E0%A4%B6&amp;oldid=5893890</t>
+  </si>
+  <si>
+    <t>ओइनवार वंश</t>
+  </si>
+  <si>
+    <t>ओइनीवार राजवंश अथवा अनवार राजवंश भारतीय उपमहाद्वीप के मिथिला क्षेत्र में शासन करने वाला एक राजवंश था जिसे सुगौना राजवंश भी कहते हैं। उन्होंने 1325 ई. और 1556 ई. के बीच इस क्षेत्र पर शासन किया। इस राजवंश से पहले इस क्षेत्र पर कर्नाट वंश का शासन था। मिथिला के कर्णाट वंशी अंतिम शासक हरिसिंह देव ने अपने योग्य मंत्री कामेश्वर ठाकुर को नवीन राजा नियुक्त किया और स्वयं नेपाल जाकर रहने लगे।</t>
+  </si>
+  <si>
+    <t>https://hi.wikipedia.org/w/index.php?title=%E0%A4%93%E0%A4%87%E0%A4%A8%E0%A4%B5%E0%A4%BE%E0%A4%B0_%E0%A4%B5%E0%A4%82%E0%A4%B6&amp;oldid=6587410</t>
+  </si>
+  <si>
+    <t>ओडेयर राजवंश</t>
+  </si>
+  <si>
+    <t>ओडियर राजवंश भारत का एक राजवंश है जो 1399 से 1761 और पुनः 1799 से 1947 मैसूर राज्य के राजवंश। ओडियर राजवंश हिन्दू थे| भारत की स्वतंत्रता के पश्चात इस राज्य को भारत में मिला लिया गया।</t>
+  </si>
+  <si>
+    <t>https://hi.wikipedia.org/w/index.php?title=%E0%A4%93%E0%A4%A1%E0%A5%87%E0%A4%AF%E0%A4%B0_%E0%A4%B0%E0%A4%BE%E0%A4%9C%E0%A4%B5%E0%A4%82%E0%A4%B6&amp;oldid=6272613</t>
+  </si>
+  <si>
+    <t>कछारी राज्य</t>
+  </si>
+  <si>
+    <t>कछारी ( असमिया : কছাৰী) मध्यकालीन असम का एक शक्तिशाली राज्य था। असम राज्य के उत्तरी असम-भूटान-सीमावर्ती कामरूप और दरंग जिले वर्तमान कछारी या 'बोड़ो' कबीले का मुख्य निवास स्थान हैं।</t>
+  </si>
+  <si>
+    <t>https://hi.wikipedia.org/w/index.php?title=%E0%A4%95%E0%A4%9B%E0%A4%BE%E0%A4%B0%E0%A5%80_%E0%A4%B0%E0%A4%BE%E0%A4%9C%E0%A5%8D%E0%A4%AF&amp;oldid=4518925</t>
+  </si>
+  <si>
+    <t>कदंब राजवंश</t>
+  </si>
+  <si>
+    <t>कदंब दक्षिण भारत का एक क्षत्रिय राजवंश था जो विद्याध्ययन के लिए कांची में रहता था और किसी पल्लव राज्यधिकारी द्वारा अपमानित होकर जिसने चौथी शदी ईसवी के मध्य (लगभग 345 ई.) प्रतिशोधस्वरूप कर्नाटक में एक छोटा सा राज्य स्थापित किया था। इस राज्य की राजधानी वैजयंती अथवा बनवासी थी। समुद्रगुप्त की दक्षिण विजय से संत्रस्त पल्लव इस राज्य की स्थापना को रोकने के लिए तत्काल हस्तक्षेप न कर सके। मयूर शर्मन्‌ के पुत्र कंग वर्मन्‌ ने वाकाटक नरेश विंध्यशक्ति द्वितीय (बासिम शाखा) के आक्रमण का सफलतापूर्वक सामना किया, तो भी उसके राज्य का कुछ क्षेत्र वाकाटकों के अधिकार में चला गया। इस कुल का सर्वाधिक शक्तिशाली राजा काकुुत्सवर्मन था जिसने इस वंश के यश तथा राज्यसीमा में पर्याप्त विस्तार किया। छठी शदी के आरंभिक दशाब्दों में रवि वर्मन्‌ राजा हुआ जिसने अपनी राजधानी बनवासी से हटाकर पालाशिका अथवा हाल्सी ( बेलगाँव जिले में) बनाई। रवि वर्मन्‌ को पल्लवों तथा गंगवंशियों से निरंतर युद्ध करना पड़ा। वातापि के चालुक्यों के उत्कर्ष का कदंब राज्य पर बहुत बुरा प्रभाव पड़ा। चालुक्यराज पुलकेशिन्‌ प्रथम ने कदंबों से उत्तरी प्रांत छीन लिए और पुलकेशिन्‌ द्वितीय ने उनको सर्वथा शक्तिहीन कर डाला। उधर कदंब राज्य के दक्षिण में स्थित गंगराज्य के राजा ने भी अवसर देखकर पुराने वैर का बदला लेने के लिए, आक्रमण किया और कदंबों के दक्षिणी प्रांतों पर अधिकार कर लिया। फिर भी कदंब वंश का अंत न हुआ और 10वीं शती के अंतिम चरण में राष्ट्रकूटों के पतन के बाद उन्होंने एक बार पुन: सिर उठाया। 13वीं शती के अंत तक कदंबों की अनेक छोटी-छोटी शाखाएँ दक्कन और कोंकण में राज करती रहीं। धारवाड़ जिले में हंगल और गोवा उनके राज्य के प्रमुख केंद्र थे। इस प्रकार लगभग एक हजार वर्ष तक कदंब दक्षिण के विभिन्न स्थानों पर गिरते पड़ते शासन करते रहे हालाँकि उनका असाधारण उत्कर्ष कभी भी संभव न हो सका।</t>
+  </si>
+  <si>
+    <t>https://hi.wikipedia.org/w/index.php?title=%E0%A4%95%E0%A4%A6%E0%A4%82%E0%A4%AC_%E0%A4%B0%E0%A4%BE%E0%A4%9C%E0%A4%B5%E0%A4%82%E0%A4%B6&amp;oldid=6285051</t>
+  </si>
+  <si>
+    <t>कलचुरि राजवंश</t>
+  </si>
+  <si>
+    <t>कलचुरि राजवंश एक शक्तिशाली भारतीय क्षत्रिय राजवंश था, जिसने मध्यभारत क्षेत्र पर शासन किया। कलचुरी राजवंश की कई शाखाएँ थीं जिन्होंने अलग-अलग शताब्दियों में अलग-अलग स्थानों से शासन किया।</t>
+  </si>
+  <si>
+    <t>https://hi.wikipedia.org/w/index.php?title=%E0%A4%95%E0%A4%B2%E0%A4%9A%E0%A5%81%E0%A4%B0%E0%A4%BF_%E0%A4%B0%E0%A4%BE%E0%A4%9C%E0%A4%B5%E0%A4%82%E0%A4%B6&amp;oldid=6611745</t>
+  </si>
+  <si>
+    <t>कलाभ्र राजवंश</t>
+  </si>
+  <si>
+    <t>कलाभ्र राजवंश ( तमिल : களப்பிரர் Kalappirar ) भारत का एक प्राचीन राजवंश था जिसने तीसरी शताब्दी से लेकर ७वीं शताब्दी तक सम्पूर्ण तमिल देश पर शासन किया। दक्षिण भारत के इतिहास में उनके शासनकाल को 'कलाभ्र अन्तर्काल' कहा जाता है। कलाभ्र शासक सम्भवतः जैन मतावलम्बी थे जिन्होने विद्रोह के द्वारा आरम्भिक चोलों , आरम्भिक पाण्ड्यों तथा चेरों के शासन का अन्त किया।</t>
+  </si>
+  <si>
+    <t>https://hi.wikipedia.org/w/index.php?title=%E0%A4%95%E0%A4%B2%E0%A4%BE%E0%A4%AD%E0%A5%8D%E0%A4%B0_%E0%A4%B0%E0%A4%BE%E0%A4%9C%E0%A4%B5%E0%A4%82%E0%A4%B6&amp;oldid=5610510</t>
+  </si>
+  <si>
+    <t>कल्होड़ा राजवंश</t>
+  </si>
+  <si>
+    <t>कल्होड़ा राजवंश ( सिन्धी : ڪلهوڙا ‎ ) सिन्ध और आधुनिक पाकिस्तान के कुछ अन्य भाग पर लगभग एक शताब्दी तक शासन करने वाला एक राजवंश था।</t>
+  </si>
+  <si>
+    <t>https://hi.wikipedia.org/w/index.php?title=%E0%A4%95%E0%A4%B2%E0%A5%8D%E0%A4%B9%E0%A5%8B%E0%A4%A1%E0%A4%BC%E0%A4%BE_%E0%A4%B0%E0%A4%BE%E0%A4%9C%E0%A4%B5%E0%A4%82%E0%A4%B6&amp;oldid=6455074</t>
+  </si>
+  <si>
+    <t>कार्कोट साम्राज्य</t>
+  </si>
+  <si>
+    <t>कर्कोट या कर्कोटक कश्मीर का एक राजवंश था, जिसने गोनंद वंश के पश्चात् कश्मीर पर अपना आधिपत्य जमाया। 'कर्कोट' पुराणों में वर्णित एक प्रसिद्ध नाग का नाम है। उसी के नाम पर इस वंश का नाम पड़ा।</t>
+  </si>
+  <si>
+    <t>https://hi.wikipedia.org/w/index.php?title=%E0%A4%95%E0%A4%BE%E0%A4%B0%E0%A5%8D%E0%A4%95%E0%A5%8B%E0%A4%9F_%E0%A4%B8%E0%A4%BE%E0%A4%AE%E0%A5%8D%E0%A4%B0%E0%A4%BE%E0%A4%9C%E0%A5%8D%E0%A4%AF&amp;oldid=6612872</t>
+  </si>
+  <si>
+    <t>कुतुबशाही राजवंश</t>
+  </si>
+  <si>
+    <t>कुतुबशाही राजवंश , दक्कन के कई इस्लामी राजवंशों की तरह, एक शिया मुस्लिम राजवंश था जिसने 1518 से 1687 तक गोलकोंडा सल्तनत पर शासन किया। इसकी जड़ें फ़ारस (आधुनिक ईरान) में थीं। प्रारंभ में वे हिंदुओं पर बहुत सख्त थे और गोलकोंडा सल्तनत में हिंदू त्योहारों को खुले तौर पर मनाने पर प्रतिबंध था। मुहम्मद कुली कुतुब शाह ने सबसे पहले इस नीति को बदला और हिंदुओं को खुले तौर पर अपने त्योहार और धर्म का पालन करने की अनुमति दी।अपने शासन के अंतिम दशकों में, कुतुब शाही राजवंश के शासकों ने शिया, सूफी और सुन्नी इस्लामी परंपराओं के साथ-साथ हिंदू परंपराओं को भी संरक्षण दिया।</t>
+  </si>
+  <si>
+    <t>https://hi.wikipedia.org/w/index.php?title=%E0%A4%95%E0%A5%81%E0%A4%A4%E0%A5%81%E0%A4%AC%E0%A4%B6%E0%A4%BE%E0%A4%B9%E0%A5%80_%E0%A4%B0%E0%A4%BE%E0%A4%9C%E0%A4%B5%E0%A4%82%E0%A4%B6&amp;oldid=6616881</t>
+  </si>
+  <si>
+    <t>कुषाण राजवंश</t>
+  </si>
+  <si>
+    <t>कुषाण राजवंश (30 ईस्वी-375 ईस्वी) का उदय बाख़्त्र क्षेत्र मे हुआ था, जिसके शासको ने फिर अपने साम्राज्य की सीमाएं मध्य एशिया से उत्तर भारत तक फैलाई। कुषाण वंश के संस्थापक कुजुल कडफिसेस था। कुछ इतिहासकार इस वंश को चीन से आए युची या युएझ़ी लोगों के मूल का मानते हैं। यह लोग खुदको आर्य मानते थे और बाख़्त्री भाषा नामक ईरानी भाषा बोलते थे, जिसे यह आर्य भाषा कहते थे।</t>
+  </si>
+  <si>
+    <t>https://hi.wikipedia.org/w/index.php?title=%E0%A4%95%E0%A5%81%E0%A4%B7%E0%A4%BE%E0%A4%A3_%E0%A4%B0%E0%A4%BE%E0%A4%9C%E0%A4%B5%E0%A4%82%E0%A4%B6&amp;oldid=6536376</t>
+  </si>
+  <si>
+    <t>कोंकण के मौर्य</t>
+  </si>
+  <si>
+    <t>मौर्य राजवंश ने चौथी और सातवीं शताब्दी के मध्य भारत के वर्तमान गोवा और महाराष्ट्र राज्यों में तटीय कोंकण क्षेत्र पर शासन किया। उनकी राजधानी का नाम पुरी थी, जिसे विभिन्न रूप से घारापुरी (एलेफंटा साल्सेट , या राजापुरी ( जंजीरा के पास) के रूप में पहचाना जाता है। राजवंश केवल कुछ प्राप्त अभिलेखों से जाना जाता है, और कालक्रम, क्षेत्र, प्रशासन और राजनीतिक स्थिति पर बहुत कम स्पष्टता प्रतीत होती है।</t>
+  </si>
+  <si>
+    <t>https://hi.wikipedia.org/w/index.php?title=%E0%A4%95%E0%A5%8B%E0%A4%82%E0%A4%95%E0%A4%A3_%E0%A4%95%E0%A5%87_%E0%A4%AE%E0%A5%8C%E0%A4%B0%E0%A5%8D%E0%A4%AF&amp;oldid=6432145</t>
+  </si>
+  <si>
+    <t>खयारवाला राजवंश</t>
+  </si>
+  <si>
+    <t>खयारवाला राजवंश भारत के बिहार और झारखंड के वर्तमान भारतीय राज्यों के कुछ भागों पर 11वीं और 12वीं शताब्दी के समय शासन करने वाला एक राजवंश था। यह खैरवार की ही एक उपजाति है उनकी राजधानी शाहाबाद जिले में खैरागढ़ में स्थित थी। रोहतास के शिलालेख के अनुसार प्रतापधवाला और श्री प्रताप इस राजवंश के प्रमुख राजा थे। इस वंश ने जपीला क्षेत्र (अब जपला ) पर गढ़ावला के सामंतों के रूप में शासन किया।</t>
+  </si>
+  <si>
+    <t>https://hi.wikipedia.org/w/index.php?title=%E0%A4%96%E0%A4%AF%E0%A4%BE%E0%A4%B0%E0%A4%B5%E0%A4%BE%E0%A4%B2%E0%A4%BE_%E0%A4%B0%E0%A4%BE%E0%A4%9C%E0%A4%B5%E0%A4%82%E0%A4%B6&amp;oldid=6362824</t>
+  </si>
+  <si>
+    <t>गंगवंश (श्वेतक)</t>
+  </si>
+  <si>
+    <t>यह गंगवंश उडीशा के श्वेतक में चिकटी (जिला गंजाम ) में राज करता था और कदाचित पूर्वी गंगवंश की कोई उपशाखा थी।</t>
+  </si>
+  <si>
+    <t>https://hi.wikipedia.org/w/index.php?title=%E0%A4%97%E0%A4%82%E0%A4%97%E0%A4%B5%E0%A4%82%E0%A4%B6_(%E0%A4%B6%E0%A5%8D%E0%A4%B5%E0%A5%87%E0%A4%A4%E0%A4%95)&amp;oldid=6366518</t>
+  </si>
+  <si>
+    <t>गजपति राजवंश</t>
+  </si>
+  <si>
+    <t>गजपति वंश आधुनिक ओडिशा क्षेत्र से भारतीय उपमहाद्वीप में शासन करने वाले राजवंश को संदर्भित करता है, जिसके शासक गजपति की उपाधि धारण करते हैं। गजपति वंश या शासन की संस्था की स्थापना पूर्वी गंग वंश के शासकों द्वारा की गई थी और इसका उपयोग बाद के राजवंशों ने किया। एक प्रमुख धार्मिक कार्य में ओडिया सांस्कृतिक क्षेत्र के देवता के रूप में भगवान जगन्नाथ का संरक्षण शामिल था।</t>
+  </si>
+  <si>
+    <t>https://hi.wikipedia.org/w/index.php?title=%E0%A4%97%E0%A4%9C%E0%A4%AA%E0%A4%A4%E0%A4%BF_%E0%A4%B0%E0%A4%BE%E0%A4%9C%E0%A4%B5%E0%A4%82%E0%A4%B6&amp;oldid=6554375</t>
+  </si>
+  <si>
+    <t>गाहड़वाल वंश</t>
+  </si>
+  <si>
+    <t>गाहड़वाल राजवंश भारतीय उपमहाद्वीप की एक क्षत्रिय शक्ति थी, जिसने ११वीं और १२वीं शताब्दी के दौरान उत्तर प्रदेश और बिहार के वर्तमान भारतीय राज्यों के कुछ हिस्सों पर शासन किया था। उनकी राजधानी वाराणसी में स्थित थी, और एक संक्षिप्त अवधि के लिए उन्होंने कान्यकुब्ज (आधुनिक कन्नौज ) पर भी शासन किया। गहड़वाल शासकों को 'काशी नरेश' के रूप में भी जाना जाता था, क्योंकि बनारस इनके राज्य की पूर्वी सीमा के निकट था।</t>
+  </si>
+  <si>
+    <t>https://hi.wikipedia.org/w/index.php?title=%E0%A4%97%E0%A4%BE%E0%A4%B9%E0%A4%A1%E0%A4%BC%E0%A4%B5%E0%A4%BE%E0%A4%B2_%E0%A4%B5%E0%A4%82%E0%A4%B6&amp;oldid=6625094</t>
+  </si>
+  <si>
+    <t>गुप्त राजवंश</t>
+  </si>
+  <si>
+    <t>गुप्त साम्राज्य (ल. 240/275–550 इस्वी) प्राचीन भारत का एक भारतीय साम्राज्य था। जिसने लगभग संपूर्ण उत्तर भारत पर शासन किया। इतिहासकारों द्वारा इस अवधि को भारत का स्वर्ण युग माना जाता है।</t>
+  </si>
+  <si>
+    <t>https://hi.wikipedia.org/w/index.php?title=%E0%A4%97%E0%A5%81%E0%A4%AA%E0%A5%8D%E0%A4%A4_%E0%A4%B0%E0%A4%BE%E0%A4%9C%E0%A4%B5%E0%A4%82%E0%A4%B6&amp;oldid=6516143</t>
+  </si>
+  <si>
+    <t>गुर्जर-प्रतिहार राजवंश</t>
+  </si>
+  <si>
+    <t>गुर्जर-प्रतिहार राजवंश भारतीय उपमहाद्वीप में प्राचीन एवं मध्यकालीन दौर के संक्रमण काल में साम्राज्य स्थापित करने वाला एक राजवंश था जिसके शासकों ने मध्य- उत्तर भारत के बड़े हिस्से पर मध्य-८वीं सदी से ११वीं सदी के बीच शासन किया। इस राजवंश का संस्थापक प्रथम नागभट्ट था, जिनके वंशजों ने पहले उज्जैन और बाद में कन्नौज को राजधानी बनाते हुए एक विस्तृत भूभाग पर शासन किया। नागभट्ट द्वारा ७२५ ईसवी में साम्राज्य की स्थापना से पूर्व भी गुर्जर-प्रतिहारों द्वारा मंडोर , मारवाड़ इत्यादि इलाकों में सामंतों के रूप में ६ठीं से ९वीं सदी के बीच शासन किया गया किंतु एक संगठित साम्राज्य के रूप में इसे स्थापित करने का श्रेय नागभट्ट को जाता है।</t>
+  </si>
+  <si>
+    <t>https://hi.wikipedia.org/w/index.php?title=%E0%A4%97%E0%A5%81%E0%A4%B0%E0%A5%8D%E0%A4%9C%E0%A4%B0-%E0%A4%AA%E0%A5%8D%E0%A4%B0%E0%A4%A4%E0%A4%BF%E0%A4%B9%E0%A4%BE%E0%A4%B0_%E0%A4%B0%E0%A4%BE%E0%A4%9C%E0%A4%B5%E0%A4%82%E0%A4%B6&amp;oldid=6420304</t>
+  </si>
+  <si>
+    <t>गुहिल राजवंश</t>
+  </si>
+  <si>
+    <t>गुहिल/गहलौत राजवंश एक प्रमुख राजवंश था जो भारतीय उपमहाद्वीप के राजस्थान क्षेत्र में मेवाड़ शहर में शासन करता था | इसका प्रारंभिक संंस्थापक राजा गुहादित्य थेे, जिन्होंने छटी शताब्दी में गुहिल वंंश की नींव रखी। गुुुहादित्य के पश्चात् 734 ई'. में बप्पा रावल को गुहिल वंश का वास्तविक संंस्थापक माना जाता है।</t>
+  </si>
+  <si>
+    <t>https://hi.wikipedia.org/w/index.php?title=%E0%A4%97%E0%A5%81%E0%A4%B9%E0%A4%BF%E0%A4%B2_%E0%A4%B0%E0%A4%BE%E0%A4%9C%E0%A4%B5%E0%A4%82%E0%A4%B6&amp;oldid=6611406</t>
+  </si>
+  <si>
+    <t>गोहिल राजवंश</t>
+  </si>
+  <si>
+    <t>सौराष्ट्र के गोहिल राजवंश ने सौराष्ट्र के कुछ भागों तथा वर्तमान गुजरात के कुछ भागों पर १२वीं शताब्दी में शासन किया था।</t>
+  </si>
+  <si>
+    <t>https://hi.wikipedia.org/w/index.php?title=%E0%A4%97%E0%A5%8B%E0%A4%B9%E0%A4%BF%E0%A4%B2_%E0%A4%B0%E0%A4%BE%E0%A4%9C%E0%A4%B5%E0%A4%82%E0%A4%B6&amp;oldid=5571463</t>
+  </si>
+  <si>
+    <t>ग्वालियर के तोमर</t>
+  </si>
+  <si>
+    <t>ग्वालियर के तोमर एक राजपूत राजवंश था जिन्होंने ग्वालियर का क़िला और इसके आसपास के क्षेत्रों में १४वीं से १६वीं सदी तक शासन किया। उन्हें ग्वालियर में सांस्कृतिक गतिविधियों को संरक्षण देने के लिए जाना जाता है।</t>
+  </si>
+  <si>
+    <t>https://hi.wikipedia.org/w/index.php?title=%E0%A4%97%E0%A5%8D%E0%A4%B5%E0%A4%BE%E0%A4%B2%E0%A4%BF%E0%A4%AF%E0%A4%B0_%E0%A4%95%E0%A5%87_%E0%A4%A4%E0%A5%8B%E0%A4%AE%E0%A4%B0&amp;oldid=6461931</t>
+  </si>
+  <si>
+    <t>चन्द्र राजवंश</t>
+  </si>
+  <si>
+    <t>चंद्र राजवंश दसवीं और ग्यारहवीं शताब्दी में भारत पर शासन करने वाला एक एक बौद्ध राजवंश था। इसने भारतीय उपमहाद्वीप के बंगाल समतट क्षेत्र तथा उत्तरी अराकान पर शासन किया। चंद्र शासन के समय ही बंगाल के उत्तर में एक और शक्तिशाली पाल वंश का शासन था।</t>
+  </si>
+  <si>
+    <t>https://hi.wikipedia.org/w/index.php?title=%E0%A4%9A%E0%A4%A8%E0%A5%8D%E0%A4%A6%E0%A5%8D%E0%A4%B0_%E0%A4%B0%E0%A4%BE%E0%A4%9C%E0%A4%B5%E0%A4%82%E0%A4%B6&amp;oldid=5774994</t>
+  </si>
+  <si>
+    <t>चालुक्य राजवंश</t>
+  </si>
+  <si>
+    <t>चालुक्य राजवंश प्राचीन भारत का एक प्रसिद्ध राजवंश है। इनकी राजधानी बादामी (वातापि) थी। अपने महत्तम विस्तार के समय (सातवीं सदी) यह वर्तमान समय के संपूर्ण कर्नाटक , पश्चिमी महाराष्ट्र , दक्षिणी मध्य प्रदेश , तटीय दक्षिणी गुजरात तथा पश्चिमी आंध्र प्रदेश में फैला हुआ था।</t>
+  </si>
+  <si>
+    <t>https://hi.wikipedia.org/w/index.php?title=%E0%A4%9A%E0%A4%BE%E0%A4%B2%E0%A5%81%E0%A4%95%E0%A5%8D%E0%A4%AF_%E0%A4%B0%E0%A4%BE%E0%A4%9C%E0%A4%B5%E0%A4%82%E0%A4%B6&amp;oldid=6022946</t>
+  </si>
+  <si>
+    <t>चुटु राजवंश</t>
+  </si>
+  <si>
+    <t>चुटु वंश के शासकों ने दक्षिण भारत के कुछ भागों पर ईसा पूर्व पहली शताब्दी से लेकर तीसरी शताब्दी (ईसा पश्चात) तक शासन किया। उनकी राजधानी वर्तमान कर्नाटक के उत्तर कन्नड जिले के बनवासी में थी। अशोक के शिलालेखों को छोड़ दें तो चुटु शासकों के शिलालेख ही कर्नाटक से प्राप्त सबसे प्राचीन शिलालेख हैं।</t>
+  </si>
+  <si>
+    <t>https://hi.wikipedia.org/w/index.php?title=%E0%A4%9A%E0%A5%81%E0%A4%9F%E0%A5%81_%E0%A4%B0%E0%A4%BE%E0%A4%9C%E0%A4%B5%E0%A4%82%E0%A4%B6&amp;oldid=6115154</t>
+  </si>
+  <si>
+    <t>चोड</t>
+  </si>
+  <si>
+    <t>चोड आंध्रप्रदेश का एक राजपरिवार था जिसने आंध्र प्रदेश के कुछ भागों पर १२वीं शताब्दी में शासन किया। वे चोलों और पश्चिमी चालुक्यों के जागीरदार थे। उनका राज्य वर्तमान गुंटूर जिले के वेलानाडु क्षेत्र में था।</t>
+  </si>
+  <si>
+    <t>https://hi.wikipedia.org/w/index.php?title=%E0%A4%9A%E0%A5%8B%E0%A4%A1&amp;oldid=6208522</t>
+  </si>
+  <si>
+    <t>चोल राजवंश</t>
+  </si>
+  <si>
+    <t>चोल ( तमिल - சோழர்) प्राचीन भारत का एक राजवंश था। दक्षिण भारत में और पास के अन्य देशों में तमिल चोल शासकों ने 9 वीं शताब्दी से 13 वीं शताब्दी के बीच एक अत्यंत शक्तिशाली हिन्दू साम्राज्य का निर्माण किया।</t>
+  </si>
+  <si>
+    <t>https://hi.wikipedia.org/w/index.php?title=%E0%A4%9A%E0%A5%8B%E0%A4%B2_%E0%A4%B0%E0%A4%BE%E0%A4%9C%E0%A4%B5%E0%A4%82%E0%A4%B6&amp;oldid=6417065</t>
+  </si>
+  <si>
+    <t>चौहान वंश</t>
+  </si>
+  <si>
+    <t>चौहान वंश (चाहमान वंश) एक भारतीय राजवंश था जिसके शासकों ने वर्तमान राजस्थान , गुजरात एवं इसके समीपवर्ती क्षेत्रों पर ७वीं शताब्दी से लेकर १२वीं शताब्दी तक शासन किया। उनके द्वारा शासित क्षेत्र 'सपादलक्ष' कहलाता था। वे चरणमान (चौहान) कबीले के सबसे प्रमुख शासक परिवार थे। मध्ययुगीन किंवदंतियों के अनुसार वे अग्निवंशी थे जो बाद में राजपूत समूह में मिल गए ।</t>
+  </si>
+  <si>
+    <t>https://hi.wikipedia.org/w/index.php?title=%E0%A4%9A%E0%A5%8C%E0%A4%B9%E0%A4%BE%E0%A4%A8_%E0%A4%B5%E0%A4%82%E0%A4%B6&amp;oldid=6388833</t>
+  </si>
+  <si>
+    <t>ज़ामोरिन</t>
+  </si>
+  <si>
+    <t>ज़ामोरिन (Zamorin), जिसे मलयालम भाषा में सामूतिरि (സാമൂതിരി) कहा जाता है, मध्यकालीन केरल के कोड़िकोड क्षेत्र के हिन्दू नरेश की उपाधि हुआ करती थी। यह संस्कृत के "स्वामी" और "श्री" (मलयालम में "तिरि") को जोड़कर उत्पन्न हुआ शब्द था। अपने चरम पर ज़ामोरिनों का शासन मालाबार तट पर कोल्लम से लेकर कोईलांडी तक विस्तारित था।</t>
+  </si>
+  <si>
+    <t>https://hi.wikipedia.org/w/index.php?title=%E0%A4%9C%E0%A4%BC%E0%A4%BE%E0%A4%AE%E0%A5%8B%E0%A4%B0%E0%A4%BF%E0%A4%A8&amp;oldid=6480135</t>
+  </si>
+  <si>
+    <t>टांक राज्य</t>
+  </si>
+  <si>
+    <t>टांक राज्य (जिसे टाक्का या टाकी के नाम से भी जाना जाता है) 6वीं से 10वीं शताब्दी ई. तक पंजाब में स्थित एक राज्य था। यह राज्य कश्मीर के दक्षिण में, सिंध के उत्तर में और ज़ुन्बिल राजवंश के पूर्व में स्थित था, जो पश्चिम में सिंधु से लेकर पूर्व में विपाशा नदी तक फैला हुआ था, जो आधुनिक सियालकोट के आसपास केंद्रित था।</t>
+  </si>
+  <si>
+    <t>https://hi.wikipedia.org/w/index.php?title=%E0%A4%9F%E0%A4%BE%E0%A4%82%E0%A4%95_%E0%A4%B0%E0%A4%BE%E0%A4%9C%E0%A5%8D%E0%A4%AF&amp;oldid=6453938</t>
+  </si>
+  <si>
+    <t>डोगरा राजवंश</t>
+  </si>
+  <si>
+    <t>डोगरा राजवंश , उत्तर भारत का एक राजवंश था। इसकी स्थापना महाराजा गुलाब सिंह ने की थी।</t>
+  </si>
+  <si>
+    <t>https://hi.wikipedia.org/w/index.php?title=%E0%A4%A1%E0%A5%8B%E0%A4%97%E0%A4%B0%E0%A4%BE_%E0%A4%B0%E0%A4%BE%E0%A4%9C%E0%A4%B5%E0%A4%82%E0%A4%B6&amp;oldid=6479363</t>
+  </si>
+  <si>
+    <t>तुलुव राजवंश</t>
+  </si>
+  <si>
+    <t>तुलुव विजयनगर साम्राज्य का तीसरा राजवंश था।</t>
+  </si>
+  <si>
+    <t>https://hi.wikipedia.org/w/index.php?title=%E0%A4%A4%E0%A5%81%E0%A4%B2%E0%A5%81%E0%A4%B5_%E0%A4%B0%E0%A4%BE%E0%A4%9C%E0%A4%B5%E0%A4%82%E0%A4%B6&amp;oldid=6449951</t>
+  </si>
+  <si>
+    <t>तैमूरी राजवंश</t>
+  </si>
+  <si>
+    <t>तैमूरी राजवंश ( फ़ारसी : ایران و توران ), स्वयंभू तुर्की-मंगोल नस्ल का एक सुन्नी मुसलमान साम्राज्य था जिसने मध्य एशिया और उत्तरी भारतीय उपमहाद्वीप के विस्तृत इलाक़ों पर राज किया। अपने चरम पर इसके साम्राज्य में समस्त ईरान , अफ़्ग़ानिस्तान और उज़बेकिस्तान के साथ-साथ पाकिस्तान , उत्तर भारत , आनातोलिया , कॉकस और मेसोपोटामिया के बड़े भूभाग शामिल थे। इस राजवंश की नीव १४वीं शताब्दी ईसवी में तैमूरलंग नामक आक्रामक और विजेता ने रखी थी। १६वीं सदी में उज़बेकिस्तान की फ़रग़ना वादी से भारत पर आक्रमण करके मुग़ल सलतनत की स्थापना करने वाले बाबर भी इसी तैमूरी राजवंश का हिस्सा था। क्योंकि तैमूरलंग को अक्सर 'अमीर तैमूर' कहा जाता था इसलिए इस राजघराने के वंशज अपने नामों में अक्सर 'मिर्ज़ा' जोड़ लिया करते थे जो 'अमीरज़ादा' (यानि 'अमीर का पुत्र') का संक्षिप्त रूप है।</t>
+  </si>
+  <si>
+    <t>https://hi.wikipedia.org/w/index.php?title=%E0%A4%A4%E0%A5%88%E0%A4%AE%E0%A5%82%E0%A4%B0%E0%A5%80_%E0%A4%B0%E0%A4%BE%E0%A4%9C%E0%A4%B5%E0%A4%82%E0%A4%B6&amp;oldid=6595993</t>
+  </si>
+  <si>
+    <t>देव राजवंश</t>
+  </si>
+  <si>
+    <t>देव राजवंश ( 12वीं - 13वीं शताब्दी) एक हिन्दू राजवंश था। जिसकी उत्पत्ति भारत के बंगाल क्षेत्र में हुई थी। इस राजवंश ने सेना राजवंश के बाद पूर्वी बंगाल पर शासन किया। राजवंश की राजधानी वर्तमान में बांग्लादेश के मुंशीगंज जनपद में बिक्रमपुर थी।</t>
+  </si>
+  <si>
+    <t>https://hi.wikipedia.org/w/index.php?title=%E0%A4%A6%E0%A5%87%E0%A4%B5_%E0%A4%B0%E0%A4%BE%E0%A4%9C%E0%A4%B5%E0%A4%82%E0%A4%B6&amp;oldid=5373353</t>
+  </si>
+  <si>
+    <t>देवगिरि के यादव</t>
+  </si>
+  <si>
+    <t>देवगिरि के यादव या सेउना यादव ( कन्नड : ಸೇವುಣರು (सेवुणरु), मराठी : देवगिरीचे यादव) (850–1334) भारत का एक राजवंश था जिसने अपने चरमोत्कर्ष काल में तुंगभद्रा से लेकर नर्मदा तक के भूभाग पर शासन किया जिसमें वर्तमान महाराष्ट्र , उत्तरी कर्नाटक , मध्य प्रदेश के कुछ भाग शामिल थे। उनकी राजधानी सिन्नर और बाद में देवगिरि हुई जो वर्तमान में दौलताबाद के नाम से जानी जाती है।</t>
+  </si>
+  <si>
+    <t>https://hi.wikipedia.org/w/index.php?title=%E0%A4%A6%E0%A5%87%E0%A4%B5%E0%A4%97%E0%A4%BF%E0%A4%B0%E0%A4%BF_%E0%A4%95%E0%A5%87_%E0%A4%AF%E0%A4%BE%E0%A4%A6%E0%A4%B5&amp;oldid=6616088</t>
+  </si>
+  <si>
+    <t>नंद वंश</t>
+  </si>
+  <si>
+    <t>नंद वंश या नंद साम्राज्य प्राचीन भारत का एक राजवंश था। यह वंश मगध पर शासन करने वाला पाँचवा राजवंश था। नंद राजवंश के शासनकाल मे ही मगध पहली बार एक साम्राज्य बन सका। नंद राजवंश मे कुल दस राजाओं द्वारा लगभग 345/344 से 323/322 ई.पू मे 23 वर्षों तक शासन किया था। नंद राजवंश की स्थापना 345 ई.पू. में महापद्मनंद के द्वारा शिशुनाग वंश के अंतिम शासक महाराजा महानन्दि की हत्या करने के बाद की गई थी। इस राजवंश का अंतिम शासक धनानन्द था। सम्राट चंद्रगुप्त मौर्य धनानंद को पराजित कर मौर्य साम्राज्य की नींव रखी। पुराणों में नंद राजवंश के प्रथम शासक को 'महापद्मनन्द' कहा गया है तथा सर्वक्षत्रान्तक आदि उपाधियों से विभूषित किया गया है। उसने पाँचवीं-चौथी शताब्दी ई.पू. उत्तरी भारत के विशाल भाग पर शासन किया। भारतीय इतिहास में पहली बार एक ऐसे साम्राज्य की स्थापना हुई जो कुलीन नहीं था तथा जिसकी सीमाएं गंगा के मैदानों को लांघ गई। यह साम्राज्य एक-रात की छत्रछाया में एक अखंड राजतंत्र था, जिसके पास अपार सैन्यबल, धनबल और जनबल था। महापद्मनंद ने निकटवर्ती सभी राजवंशो को जीतकर एक विशाल साम्राज्य की स्थापना की एवं केंद्रीय शासन की व्यवस्था लागू की। इसीलिए सम्राट महापदम नंद को "केंद्रीय शासन पद्धति का जनक" कहा जाता है।</t>
+  </si>
+  <si>
+    <t>https://hi.wikipedia.org/w/index.php?title=%E0%A4%A8%E0%A4%82%E0%A4%A6_%E0%A4%B5%E0%A4%82%E0%A4%B6&amp;oldid=6629293</t>
+  </si>
+  <si>
+    <t>नद्दुल चाहमान राजवंश</t>
+  </si>
+  <si>
+    <t>नद्दुल के चाहमान जो नाडोल के चौहान कोलिय के नाम से भी जाने जाते हैं प्राचीन में भारत का एक राजवंश था नद्दुल जो अब नाडोल नाम से है और यह क्षेत्र वर्तमान में भारत के राजस्थान राज्य के पाली ज़िले में स्थित है। ये चौहान वंश से है इस वंश के स्थापक लक्ष्मण है जो लाखा के नाम से जाने जाते थे। जबकि अंतिम शासक जयतासिंह थे इनका निधन एक युद्ध में 1197 ईस्वी में हो गया था।</t>
+  </si>
+  <si>
+    <t>https://hi.wikipedia.org/w/index.php?title=%E0%A4%A8%E0%A4%A6%E0%A5%8D%E0%A4%A6%E0%A5%81%E0%A4%B2_%E0%A4%9A%E0%A4%BE%E0%A4%B9%E0%A4%AE%E0%A4%BE%E0%A4%A8_%E0%A4%B0%E0%A4%BE%E0%A4%9C%E0%A4%B5%E0%A4%82%E0%A4%B6&amp;oldid=6020799</t>
+  </si>
+  <si>
+    <t>नल राजवंश</t>
+  </si>
+  <si>
+    <t>नल एक भारतीय राजवंश था जिसने 6वीं शताब्दी ईस्वी के दौरान वर्तमान छत्तीसगढ़ और ओडिशा के कुछ हिस्सों पर शासन किया। उनका मुख्य क्षेत्र बस्तर और कोरापूत जिलों के आसपास के इलाकों में शामिल था। उनकी राजधानी संभवतः पुष्करी थी, जिसकी पहचान बस्तर जिले के आधुनिक गढ़धनोरा से की जाती है। एक समय पर, ऐसा प्रतीत होता है कि उन्होंने विदर्भ क्षेत्र में वाकाटक राजधानी नन्दिवर्धन पर विजय प्राप्त की थी, लेकिन बाद में वाकाटकों के साथ-साथ चालुक्यों के विरुद्ध भी उन्हें पराजयों का सामना करना पड़ा। उनके उत्तरी पड़ोसी शरभपुरिया राजवंश ने भी उनके पतन में भूमिका निभाई प्रतीत होती है। संभवतः उनका स्थान पाण्डुवंशी राजवंश ने ले लिया, हालांकि राजवंश की एक शाखा 7वीं या 8वीं शताब्दी ईस्वी तक एक छोटे से क्षेत्र पर शासन करती रही प्रतीत होती है।</t>
+  </si>
+  <si>
+    <t>https://hi.wikipedia.org/w/index.php?title=%E0%A4%A8%E0%A4%B2_%E0%A4%B0%E0%A4%BE%E0%A4%9C%E0%A4%B5%E0%A4%82%E0%A4%B6&amp;oldid=6611440</t>
+  </si>
+  <si>
+    <t>नाग (वंश)</t>
+  </si>
+  <si>
+    <t>नाग भारत भूमि विभिन्न मानवीय जातियो तथा संस्कृतियों का अजायब घर है। नाग जातियां अपनी मानवीय विशेषताओ के चलते सम्पूर्ण भारत मे पूजनीय रही है। सर्वशक्तिमान ईश्वर "शिव "नाम से सभी मनुष्यों समान रूप से विद्यमान है जो नारी में श्रद्धा रूप में तथा परुषों में विश्वास रूप में होता है। 'भगवान शिव'नाग जातियो के सभी वंशो के पूजनीय है।भगवान शिव पर विश्वास कर उनकी पूजा करने वालो को शैवधर्मी तथा ऐसे धर्म को शैवधर्म कहते है,तथा इस धर्म से सम्बंधित ग्रन्थों को शैव धर्मशास्त्र कहते है। शैवधर्म शुद्ध वैज्ञानिक एवं आध्यात्मिक धर्म है जो मनुष्य को मानवता और आध्यात्मिकता के उच्च गुण की ओर ले जाकर मनुष्य का कल्याण करने वाला है।शैव धर्मशास्त्रो में 'शिव 'ने मनुष्य को ही श्रेष्ठ माना है।शैवधर्म और वैष्णव धर्म हमेशा ही प्रतिद्वंद्वी रहे है।शैवधर्म ,जहाँ लोकधर्म जनसामान्य का धर्म रहा है वही वैष्णव धर्म राजसी और व्यापारियों का धर्म रहा है।शैवशास्त्रों में वर्णन है कि जब कलियुग में वैष्णव धर्मी संरक्षक भगवान विष्णु नर रूप में ब्राह्मण के घर अवतार लेंगे तब भगवान शिव के गण शैवधर्म की शिक्षाओं का प्रसार कर रहे होंगे। नाग जाति के लोग शिव के अतिरिक्त किसी को अपना आराध्य नही मानते है।</t>
+  </si>
+  <si>
+    <t>https://hi.wikipedia.org/w/index.php?title=%E0%A4%A8%E0%A4%BE%E0%A4%97_(%E0%A4%B5%E0%A4%82%E0%A4%B6)&amp;oldid=6558476</t>
+  </si>
+  <si>
+    <t>नायक राजवंश</t>
+  </si>
+  <si>
+    <t>काकतीय और विजयनगर साम्राज्य के दौरान नायक राजवंशों का उदय हुआ। नायक मूल रूप से विजयनगर साम्राज्य के अधीन सैन्य गवर्नर थे। तालिकोट का युद्ध के बाद, उनमें से कई ने खुद को स्वतंत्र घोषित कर दिया।</t>
+  </si>
+  <si>
+    <t>https://hi.wikipedia.org/w/index.php?title=%E0%A4%A8%E0%A4%BE%E0%A4%AF%E0%A4%95_%E0%A4%B0%E0%A4%BE%E0%A4%9C%E0%A4%B5%E0%A4%82%E0%A4%B6&amp;oldid=6223601</t>
+  </si>
+  <si>
+    <t>नारायणगढ़ राज</t>
+  </si>
+  <si>
+    <t>नारायणगढ़ राज, जिसे नारायणगढ़ साम्राज्य के नाम से भी जाना जाता है, एक मध्ययुगीन अर्ध-स्वतंत्र राज्य था जो बाद में पश्चिम बंगाल के तत्कालीन मिदनापुर जिले में ब्रिटिश राज के दौरान सदगोप की एक बड़ी जमींदारी संपत्ति बन गया। इस राज्य का क्षेत्रफल 126.96 वर्ग मील था, जिसमें 387 गाँव शामिल थे।</t>
+  </si>
+  <si>
+    <t>https://hi.wikipedia.org/w/index.php?title=%E0%A4%A8%E0%A4%BE%E0%A4%B0%E0%A4%BE%E0%A4%AF%E0%A4%A3%E0%A4%97%E0%A4%A2%E0%A4%BC_%E0%A4%B0%E0%A4%BE%E0%A4%9C&amp;oldid=6018509</t>
+  </si>
+  <si>
+    <t>पनार (तराई के राजा)</t>
+  </si>
+  <si>
+    <t>उन्होंने सम्राट महाबली के मार्ग पर प्रकट होने का दावा किया।</t>
+  </si>
+  <si>
+    <t>https://hi.wikipedia.org/w/index.php?title=%E0%A4%AA%E0%A4%A8%E0%A4%BE%E0%A4%B0_(%E0%A4%A4%E0%A4%B0%E0%A4%BE%E0%A4%88_%E0%A4%95%E0%A5%87_%E0%A4%B0%E0%A4%BE%E0%A4%9C%E0%A4%BE)&amp;oldid=5664494</t>
+  </si>
+  <si>
+    <t>परिव्राजक राजवंश</t>
+  </si>
+  <si>
+    <t>परिव्राजक राजवंश ने 5वीं और 6वीं शताब्दी के दौरान मध्य भारत के कुछ भागों पर शासन किया। इस राजवंश के राजाओं को महाराजा की उपाधि दी गई थी, और संभवतः गुप्त साम्राज्य के सामंतों के रूप में शासन किया। हस्तिन और संक्षोभ नामक इस वंश के दो राजाओं के शिलालेखों से इस राजवंश के बारे में जानकारी प्राप्त होती है।</t>
+  </si>
+  <si>
+    <t>https://hi.wikipedia.org/w/index.php?title=%E0%A4%AA%E0%A4%B0%E0%A4%BF%E0%A4%B5%E0%A5%8D%E0%A4%B0%E0%A4%BE%E0%A4%9C%E0%A4%95_%E0%A4%B0%E0%A4%BE%E0%A4%9C%E0%A4%B5%E0%A4%82%E0%A4%B6&amp;oldid=6520807</t>
+  </si>
+  <si>
+    <t>पल्लव राजवंश</t>
+  </si>
+  <si>
+    <t>पल्लव राजवंश प्राचीन दक्षिण भारत का राजवंश था ।चौथी शताब्दी में इसने कांचीपुरम में राज्य स्थापित किया और लगभग ६०० वर्ष तमिल और तेलुगु क्षेत्र में राज्य किया।</t>
+  </si>
+  <si>
+    <t>https://hi.wikipedia.org/w/index.php?title=%E0%A4%AA%E0%A4%B2%E0%A5%8D%E0%A4%B2%E0%A4%B5_%E0%A4%B0%E0%A4%BE%E0%A4%9C%E0%A4%B5%E0%A4%82%E0%A4%B6&amp;oldid=6582344</t>
+  </si>
+  <si>
+    <t>पश्चिम गंग वंश</t>
+  </si>
+  <si>
+    <t>पश्चिम गंग वंश (३५०-१००० ई.) ( कन्नड़ : ಪಶ್ಚಿಮ ಗಂಗ ಸಂಸ್ಥಾನ ) प्राचीन कर्नाटक का एक राजवंश था। ये पूर्वी गंग वंश से अलग थे। पूर्वी गंग जिन्होंने बाद के वर्षों में ओडिशा पर राज्य किया। आम धारण के अनुसार पश्चिम गंग वंश ने शसन तब संभाला जब पल्लव वंश के पतन उपरांत बहुत से स्वतंत्र शासक उठ खड़े हुए थे। इसका एक कारण समुद्रगुप्त से युद्ध भी रहे थे। इस वंश ने ३५० ई से ५५० ई तक सार्वभौम राज किया था। इनकी राजधानी पहले कोलार रही जो समय के साथ बदल कर आधुनिक युग के मैसूर जिला में कावेरी नदी के तट पर तालकाड स्थानांतरित हो गयी थी।</t>
+  </si>
+  <si>
+    <t>https://hi.wikipedia.org/w/index.php?title=%E0%A4%AA%E0%A4%B6%E0%A5%8D%E0%A4%9A%E0%A4%BF%E0%A4%AE_%E0%A4%97%E0%A4%82%E0%A4%97_%E0%A4%B5%E0%A4%82%E0%A4%B6&amp;oldid=6337657</t>
+  </si>
+  <si>
+    <t>पाण्ड्य राजवंश</t>
+  </si>
+  <si>
+    <t>पाण्ड्य राजवंश ( तमिल : பாண்டியர்) प्राचीन भारत का एक राजवंश था। इसने भारत में 560 से 1300 ई तक राज किया।</t>
+  </si>
+  <si>
+    <t>https://hi.wikipedia.org/w/index.php?title=%E0%A4%AA%E0%A4%BE%E0%A4%A3%E0%A5%8D%E0%A4%A1%E0%A5%8D%E0%A4%AF_%E0%A4%B0%E0%A4%BE%E0%A4%9C%E0%A4%B5%E0%A4%82%E0%A4%B6&amp;oldid=6317575</t>
+  </si>
+  <si>
+    <t>पाल वंश</t>
+  </si>
+  <si>
+    <t>पाल साम्राज्य मध्यकालीन उत्तर भारत का सबसे शक्तिशाली और महत्वपूर्ण साम्राज्य माना जाता है, जो कि 750-1174 इसवी तक चला। यह पूर्व- मध्यकालीन राजवंश था। इस वंश के शासकों ने भारत के पूर्वी भाग में एक विशाल साम्राज्य बनाया। जब हर्षवर्धन काल के बाद समस्त उत्तरी भारत में राजनीतिक, सामाजिक एवं आर्थिक गहरा संकट उत्पनन्न हो गया, तब बिहार , बंगाल और उड़ीसा के सम्पूर्ण क्षेत्र में पूरी तरह अराजकत फैली थी। पाल साम्राज्य की नींव 750 ई. में राजा गोपाल पाल ने डाली। बताया जाता है कि उस क्षेत्र में फैली अशान्ति को दबाने के लिए कुछ प्रमुख लोगों ने उसको राजा के रूप में चुना। इस प्रकार राजा का निर्वाचन एक अभूतपूर्व घटना थी। इसका अर्थ शायद यह है कि गोपाल उस क्षेत्र के सभी महत्त्वपूर्ण लोगों का समर्थन प्राप्त करने में सफल हो सका और इससे उसे अपनी स्थिति मज़बूत करन में काफ़ी सहायता मिली।</t>
+  </si>
+  <si>
+    <t>https://hi.wikipedia.org/w/index.php?title=%E0%A4%AA%E0%A4%BE%E0%A4%B2_%E0%A4%B5%E0%A4%82%E0%A4%B6&amp;oldid=6418363</t>
+  </si>
+  <si>
+    <t>पुष्पभूति</t>
+  </si>
+  <si>
+    <t>पुष्पभूति प्राचीन भारत का प्रसिद्ध राजवंश था जिसने लगभग छठी शताब्दी के अंत से लेकर लगभग सातवीं शताब्दी के मध्य तक राज्य किया। बाणभट्ट के अनुसार इस वंश का संस्थापक पुष्पभूति था। वह श्रीकंठ जनपद का राजा था तथा स्थाणीश्वर उसकी राजधानी थी। बाण ने बताया है, श्रीकंठ जनपद का नाम श्रीकंठ नामक नाग पर पड़ा (हर्षचरित्‌ 267-268, जीवानंद संस्करण)। श्रीकंठ जलपद का राजा पुष्पभूति वीर, साहसी, नीतिवान्‌, तथा प्रजापालक था। वह शैव धर्मावलंबी था। उनके गुरु भैरवाचार्य दाक्षिणात्य महाशैव मत के माननेवाले थे। पुष्पभूति ने उन भैरवाचार्य के कहने पर महाकालहृदय नामक महामंत्र महाश्मशान में एक कोटि जप किया था। भैरवाचार्य ने पुष्पभूति को अट्टहास नामक तलवार भी दी। राजा की शिव के प्रति असीम और अखंड भक्ति जानकर स्वयं लक्ष्मी ने वरदान दिया- 'तुम महान्‌ राजवंश के संस्थापक बनोगे जिस राजवंश में हरिश्चंद्र की भाँति समस्त द्वीपों का भोग करनेवाला हर्ष नामक चक्रवर्ती जन्म लेगा ( हर्षचरित‌ 322,329)।</t>
+  </si>
+  <si>
+    <t>https://hi.wikipedia.org/w/index.php?title=%E0%A4%AA%E0%A5%81%E0%A4%B7%E0%A5%8D%E0%A4%AA%E0%A4%AD%E0%A5%82%E0%A4%A4%E0%A4%BF&amp;oldid=5717261</t>
+  </si>
+  <si>
+    <t>पूर्वी गंगवंश</t>
+  </si>
+  <si>
+    <t>पूर्वी गंगवंश (ओड़िया : ଗଙ୍ଗ ବଂଶ ଶାସନ/गंग बंश शासन) भारतीय उपमहाद्वीप का एक हिन्दू राजवंश था। उन्होने कलिंग को राजधानी बनाया। उनके राज्य के अन्तर्गत वर्तमान समय का सम्पूर्ण उड़ीसा तो था ही, इसके साथ ही पश्चिम बंगाल , आन्ध्र प्रदेश तथा छत्तीसगढ़ के भी कुछ भाग थे।इनका शासन ११वीं शताब्दी से १५वीं शताब्दी तक रहा। उनकी राजधानी का नाम 'कलिंगनगर' था जो वर्तमान समय में आन्ध्र प्रदेश के श्रीकाकुलम जिला का श्रीमुखलिंगम है। पहले यह उड़ीसा के गंजम जिले में था। पूर्वी गंगवंश के शासक कोणार्क के सूर्य मन्दिर के निर्माण के लिये प्रसिद्ध हैं।</t>
+  </si>
+  <si>
+    <t>https://hi.wikipedia.org/w/index.php?title=%E0%A4%AA%E0%A5%82%E0%A4%B0%E0%A5%8D%E0%A4%B5%E0%A5%80_%E0%A4%97%E0%A4%82%E0%A4%97%E0%A4%B5%E0%A4%82%E0%A4%B6&amp;oldid=6631841</t>
+  </si>
+  <si>
+    <t>पेरुमल</t>
+  </si>
+  <si>
+    <t>पेरुमल ('महान') एक हिन्दू देवता का नाम है।</t>
+  </si>
+  <si>
+    <t>https://hi.wikipedia.org/w/index.php?title=%E0%A4%AA%E0%A5%87%E0%A4%B0%E0%A5%81%E0%A4%AE%E0%A4%B2&amp;oldid=6492980</t>
+  </si>
+  <si>
+    <t>फारूक़ी राजवंश</t>
+  </si>
+  <si>
+    <t>फारूकी राजवंश या खानदेश सल्तनत : जिसे फारूक शाही राजवंश के नाम से भी जाना जाता है, खानदेश सल्तनत (खानदेश क्षेत्र के नाम पर) का एक शासक अरब राजवंश था जो 1382 में इसकी स्थापना से लेकर 1601 में मुगल सम्राट अकबर द्वारा इसके विलय तक चला। इस राजवंश के संस्थापक मलिक अहमद (जिन्हें मलिक राजा के नाम से भी जाना जाता है) ने अपने प्रारंभिक वर्षों में बहमनी शासक मुहम्मद शाह प्रथम के खिलाफ विद्रोह में भाग लिया था। जब उन्हें दक्कन से भागने के लिए विवश होना पड़ा तो उन्होंने ताप्ती नदी के किनारे स्थित थालनेर (वर्तमान महाराष्ट्र के धुले जिले में) में अपना निवास स्थान बनाया। थलनेर और करांडा (वर्तमान कारवंद) की जागीरों का अनुदान प्राप्त करने के बाद1370 में फ़िरोज़ शाह तुगलक से थालनेर के उत्तर में किमी) क्षेत्र पर विजय प्राप्त की जिसे बाद में खानदेश (खानों की भूमि) के नाम से जाना गया। 1382 तक उन्होंने स्वतंत्र रूप से शासन करना शुरू कर दिया था।</t>
+  </si>
+  <si>
+    <t>https://hi.wikipedia.org/w/index.php?title=%E0%A4%AB%E0%A4%BE%E0%A4%B0%E0%A5%82%E0%A4%95%E0%A4%BC%E0%A5%80_%E0%A4%B0%E0%A4%BE%E0%A4%9C%E0%A4%B5%E0%A4%82%E0%A4%B6&amp;oldid=6602347</t>
+  </si>
+  <si>
+    <t>भौम राजवंश</t>
+  </si>
+  <si>
+    <t>दानव राजवंश के बाद, भौम वंश प्रागज्योतिष का दूसरा पौराणिक राजवंश है। नरकासुर , जिनके बारे में कहा जाता है कि उन्होंने इस राजवंश की स्थापना की। वंशज भगदत्त और वज्रदत्त का उल्लेख सबसे पहले महाभारत और रामायण में हुआ है।</t>
+  </si>
+  <si>
+    <t>https://hi.wikipedia.org/w/index.php?title=%E0%A4%AD%E0%A5%8C%E0%A4%AE_%E0%A4%B0%E0%A4%BE%E0%A4%9C%E0%A4%B5%E0%A4%82%E0%A4%B6&amp;oldid=6221335</t>
+  </si>
+  <si>
+    <t>भौम-कर राजवंश</t>
+  </si>
+  <si>
+    <t>भौम राजवंश या कर राजवंश 8वीं से 10वीं शताब्दी के मध्य पूर्वी भारत के कुछ भागों पर शासन करने वाला एक राजवंश था। इनके राज्य का नाम "तोशल" था जिसके अन्तर्गत वर्तमान ओड़ीसा के कुछ भाग आते थे। आठवीं शताब्दी की अंत तक, भौम-करों ने पूर्व शैलोद्भव वंश के क्षेत्र पर अपना आधिपत्य स्थापित कर लिया था। इस वंश के प्रारंभिक शासक बौद्ध धर्म का पालन करते थे, जबकि इसके बाद के शासक शैव और वैष्णव धर्म का अनुसरण करने लगे थे। इस वंश के शासकों में सात महिलाएँ भी शामिल थीं। लगभग 10वीं शताब्दी में भंज और सोमवंशी राजवंश ने भौम-करों को हरा कर इस क्षेत्र में अपना राज्य स्थापित कर लिया।</t>
+  </si>
+  <si>
+    <t>https://hi.wikipedia.org/w/index.php?title=%E0%A4%AD%E0%A5%8C%E0%A4%AE-%E0%A4%95%E0%A4%B0_%E0%A4%B0%E0%A4%BE%E0%A4%9C%E0%A4%B5%E0%A4%82%E0%A4%B6&amp;oldid=6595242</t>
+  </si>
+  <si>
+    <t>मुजफ्फरिद वंश</t>
+  </si>
+  <si>
+    <t>मुज़फ़्फ़रिद वंश ने , जिसे कभी-कभी अहमद शाही भी कहा जाता है, 1391 से 1583 तक पश्चिमी भारत में गुजरात सल्तनत पर शासन किया। इस वंश के संस्थापक ज़फ़र ख़ान (बाद में मुज़फ़्फ़र शाह प्रथम ) थे, जो पहले दिल्ली सल्तनत के अधीन गुजरात के सूबेदार थे। जब 1398 में तैमूरलंग द्वारा दिल्ली को लूटे जाने के कारण दिल्ली सल्तनत कमजोर हो गई, तब ज़फ़र ख़ान ने इस अवसर का लाभ उठाकर स्वयं को स्वतंत्र गुजरात का सुल्तान स्थापित कर लिया। उनके पोते , अहमद शाह प्रथम ने राजधानी अहमदाबाद में स्थापित की। इस वंश ने लगभग 200 वर्षों तक शासन किया परन्तु 1572 में मुग़ल साम्राज्य ने गुजरात गुजरात सल्तनत पर विजय प्राप्त कर और गुजरात मुग़ल साम्राज्य का एक सूबा बन गया। महमूद बेगड़ा के शासनकाल में यह सल्तनत अपने विस्तार के चरम पर पहुँची, जहाँ इसका विस्तार पूर्व में मालवा तक और पश्चिम में कच्छ की खाड़ी तक था।</t>
+  </si>
+  <si>
+    <t>https://hi.wikipedia.org/w/index.php?title=%E0%A4%AE%E0%A5%81%E0%A4%9C%E0%A4%AB%E0%A5%8D%E0%A4%AB%E0%A4%B0%E0%A4%BF%E0%A4%A6_%E0%A4%B5%E0%A4%82%E0%A4%B6&amp;oldid=6595990</t>
+  </si>
+  <si>
+    <t>मैत्रक राजवंश</t>
+  </si>
+  <si>
+    <t>मैत्रक राजवंश ने ४७५ ई से ७६७ ई के मध्य गुजरात पर शासन किया। इस वंश का संस्थापक सेनापति भुटार्क था जो गुप्त साम्राज्य के अधीन सौराष्ट्र उपखण्ड का राज्यपाल था।</t>
+  </si>
+  <si>
+    <t>https://hi.wikipedia.org/w/index.php?title=%E0%A4%AE%E0%A5%88%E0%A4%A4%E0%A5%8D%E0%A4%B0%E0%A4%95_%E0%A4%B0%E0%A4%BE%E0%A4%9C%E0%A4%B5%E0%A4%82%E0%A4%B6&amp;oldid=6621231</t>
+  </si>
+  <si>
+    <t>रणस्तम्भपुर के चहमान</t>
+  </si>
+  <si>
+    <t>रणस्तम्भपुर के चहमान भारत का १३वीं शताब्दी का एक राजवंश था। उन्होने रणस्तम्भपुर (वर्तमान समय का रणथम्भौर ) के आसपास के क्षेत्रों पर शासन किया, जो उनकी राजधानी थी। इन्हें 'रणथम्भौर के चौहान' भी कहा जाता है।</t>
+  </si>
+  <si>
+    <t>https://hi.wikipedia.org/w/index.php?title=%E0%A4%B0%E0%A4%A3%E0%A4%B8%E0%A5%8D%E0%A4%A4%E0%A4%AE%E0%A5%8D%E0%A4%AD%E0%A4%AA%E0%A5%81%E0%A4%B0_%E0%A4%95%E0%A5%87_%E0%A4%9A%E0%A4%B9%E0%A4%AE%E0%A4%BE%E0%A4%A8&amp;oldid=6629137</t>
+  </si>
+  <si>
+    <t>राजर्षितुल्यकुल</t>
+  </si>
+  <si>
+    <t>राजर्षितुल्यकुल एक राजवंश था जिसने भारत के दक्षिण कोशल क्षेत्र पर शासन्न किया। इस राजवंश को सुर राजवंश भी कहा जाता है। इस वंश के पतन के पश्चात इस क्षेत्र में पर्वतद्वारक राजवंश का उदय हुआ।</t>
+  </si>
+  <si>
+    <t>https://hi.wikipedia.org/w/index.php?title=%E0%A4%B0%E0%A4%BE%E0%A4%9C%E0%A4%B0%E0%A5%8D%E0%A4%B7%E0%A4%BF%E0%A4%A4%E0%A5%81%E0%A4%B2%E0%A5%8D%E0%A4%AF%E0%A4%95%E0%A5%81%E0%A4%B2&amp;oldid=6207036</t>
+  </si>
+  <si>
     <t>चेर राजवंश</t>
   </si>
   <si>
-    <t>Chera dynasty</t>
-  </si>
-  <si>
-    <t>one of the three major kingdoms of ancient south India. Ruled over parts of present-day states of Kerala and Tamil Nadu in south India</t>
-  </si>
-  <si>
-    <t>करूर</t>
-  </si>
-  <si>
-    <t>राजवंश; ऐतिहासिक देश</t>
-  </si>
-  <si>
-    <t>https://www.wikidata.org/wiki/Q877155</t>
-  </si>
-  <si>
-    <t>चोल राजवंश</t>
-  </si>
-  <si>
-    <t>Chola dynasty</t>
-  </si>
-  <si>
-    <t>dynasty of southern India</t>
-  </si>
-  <si>
-    <t>पूहार, मयिलाडुतुरै</t>
-  </si>
-  <si>
-    <t>ऐतिहासिक देश</t>
-  </si>
-  <si>
-    <t>https://www.wikidata.org/wiki/Q151148</t>
-  </si>
-  <si>
-    <t>गुप्त साम्राज्य</t>
-  </si>
-  <si>
-    <t>Gupta Empire</t>
-  </si>
-  <si>
-    <t>ancient Indian empire (c. 3rd century CE–575 CE)</t>
-  </si>
-  <si>
-    <t>पाटलीपुत्र</t>
-  </si>
-  <si>
-    <t>https://www.wikidata.org/wiki/Q11774</t>
-  </si>
-  <si>
-    <t>कुषाण साम्राज्य</t>
-  </si>
-  <si>
-    <t>Kushan Empire</t>
-  </si>
-  <si>
-    <t>empire in Central and South Asia (30–375 AD)</t>
-  </si>
-  <si>
-    <t>बगराम</t>
-  </si>
-  <si>
-    <t>https://www.wikidata.org/wiki/Q25979</t>
-  </si>
-  <si>
-    <t>मराठा साम्राज्य</t>
-  </si>
-  <si>
-    <t>Maratha Empire</t>
-  </si>
-  <si>
-    <t>1674–1818 empire in the Indian subcontinent</t>
-  </si>
-  <si>
-    <t>रायगढ़</t>
-  </si>
-  <si>
-    <t>https://www.wikidata.org/wiki/Q83618</t>
-  </si>
-  <si>
-    <t>मौर्य साम्राज्य</t>
-  </si>
-  <si>
-    <t>Maurya empire</t>
-  </si>
-  <si>
-    <t>ancient Indian empire (322–184 BCE)</t>
-  </si>
-  <si>
-    <t>पाटलीपुत्र; पटना</t>
-  </si>
-  <si>
-    <t>https://www.wikidata.org/wiki/Q62943</t>
-  </si>
-  <si>
-    <t>मुग़ल साम्राज्य</t>
-  </si>
-  <si>
-    <t>Mughal Empire</t>
-  </si>
-  <si>
-    <t>great Turkic descent empire ruling India (1526–1857)</t>
-  </si>
-  <si>
-    <t>आगरा; फ़तेहपुर सीकरी; पुरानी दिल्ली; लाहौर; दिल्ली</t>
-  </si>
-  <si>
-    <t>https://www.wikidata.org/wiki/Q33296</t>
-  </si>
-  <si>
-    <t>पाल साम्राज्य</t>
-  </si>
-  <si>
-    <t>Pala Empire</t>
-  </si>
-  <si>
-    <t>kingdom In North India</t>
-  </si>
-  <si>
-    <t>https://www.wikidata.org/wiki/Q668412</t>
-  </si>
-  <si>
-    <t>पल्लव राजवंश</t>
-  </si>
-  <si>
-    <t>Pallava dynasty</t>
-  </si>
-  <si>
-    <t>Indian dynasty between the 3rd and 9th centuries CE</t>
-  </si>
-  <si>
-    <t>कांचिपुरम</t>
-  </si>
-  <si>
-    <t>ऐतिहासिक देश; राजवंश; ऐतिहासिक काल</t>
-  </si>
-  <si>
-    <t>https://www.wikidata.org/wiki/Q466803</t>
-  </si>
-  <si>
-    <t>पांड्य राजवंश</t>
-  </si>
-  <si>
-    <t>Pandya dynasty</t>
-  </si>
-  <si>
-    <t>ancient Tamil dynasty of south India</t>
-  </si>
-  <si>
-    <t>मदुरई</t>
-  </si>
-  <si>
-    <t>https://www.wikidata.org/wiki/Q844910</t>
-  </si>
-  <si>
-    <t>सातवाहन राजवंश</t>
-  </si>
-  <si>
-    <t>Satavahana dynasty</t>
-  </si>
-  <si>
-    <t>Indian dynasty (2nd century BCE–Early 3rd century CE)</t>
-  </si>
-  <si>
-    <t>अमरावति</t>
-  </si>
-  <si>
-    <t>https://www.wikidata.org/wiki/Q5257</t>
-  </si>
-  <si>
-    <t>सेन राजवंश</t>
-  </si>
-  <si>
-    <t>Sena dynasty</t>
-  </si>
-  <si>
-    <t>sena Empire</t>
-  </si>
-  <si>
-    <t>नवद्वीप</t>
-  </si>
-  <si>
-    <t>https://www.wikidata.org/wiki/Q2428714</t>
-  </si>
-  <si>
-    <t>शुंग साम्राज्य</t>
-  </si>
-  <si>
-    <t>Shunga Empire</t>
-  </si>
-  <si>
-    <t>Indian empire (184 BCE-75 BCE)</t>
-  </si>
-  <si>
-    <t>https://www.wikidata.org/wiki/Q651377</t>
-  </si>
-  <si>
-    <t>विजयनगर साम्राज्य</t>
-  </si>
-  <si>
-    <t>Vijayanagara Empire</t>
-  </si>
-  <si>
-    <t>Hindu kingdom in Southern India (14th-17th century)</t>
-  </si>
-  <si>
-    <t>विजयनगर; पेनुकोंडा; चंद्रगिरि; वेल्लोर</t>
-  </si>
-  <si>
-    <t>https://www.wikidata.org/wiki/Q167639</t>
+    <t>चेर (तमिल - சேரர்) दक्षिण भारत का एक राजवंश था। इसको ऐतरेय ब्राह्मण ग्रंथ मे "केरलपुत्र" ( संस्कृत ) नाम से भी जाना जाता है। अशोक के दूसरे शिलालेख मे उसने इसे केरलपुत्र कहा। इसका विस्तार आधुनिक कोयम्बटूर , सलेम तथा करूर जिले (तमिल नाडु) तथा मध्य केरल के कुछ क्षेत्रों के पास केन्द्रित था।</t>
+  </si>
+  <si>
+    <t>https://hi.wikipedia.org/w/index.php?title=%E0%A4%9A%E0%A5%87%E0%A4%B0_%E0%A4%B0%E0%A4%BE%E0%A4%9C%E0%A4%B5%E0%A4%82%E0%A4%B6&amp;oldid=6282257</t>
+  </si>
+  <si>
+    <t>राठौड़</t>
+  </si>
+  <si>
+    <t>राठौड़ अथवा राठौड एक राजपूत वंश है जो उत्तर भारत में निवास करते हैं। इन्हें सूर्यवंशी राजपूत माना जाता है। वे पारम्परिक रूप से राजस्थान के उत्तर-पश्चिमी क्षेत्र मारवाड़ में शासन करते थे।</t>
+  </si>
+  <si>
+    <t>https://hi.wikipedia.org/w/index.php?title=%E0%A4%B0%E0%A4%BE%E0%A4%A0%E0%A5%8C%E0%A4%A1%E0%A4%BC&amp;oldid=6615029</t>
+  </si>
+  <si>
+    <t>राय वंश</t>
+  </si>
+  <si>
+    <t>राय (489 ई - 632 ई) सिन्ध का एक हिन्दू वंश था जिसने भारतीय उपमहाद्वीप के उत्तरी-पश्चिमी भाग पर शासन किया। यह रोड़ राजवंश का उत्तराधिकारी बना। इस साम्राज्य की शिखर अवस्था में इनका प्रभाव पूरब में कश्मीर से लेकर, पश्चिम में मकरान और देबल बन्दरगाह (आधुनिक कराची ) तक, दक्षिण में सूरत बन्दरगाह तक और उत्तर में कान्धार , सुलैमान , फरदान और किकानान पहाड़ियों तक था। इनका शासन लगभग साढे पन्द्रह लाख वर्ग किलोमीतर में फैला हुआ था। इस वंश का शासन लगभग १४३ वर्ष तक रहा।</t>
+  </si>
+  <si>
+    <t>https://hi.wikipedia.org/w/index.php?title=%E0%A4%B0%E0%A4%BE%E0%A4%AF_%E0%A4%B5%E0%A4%82%E0%A4%B6&amp;oldid=6504003</t>
+  </si>
+  <si>
+    <t>राष्ट्रकूट राजवंश</t>
+  </si>
+  <si>
+    <t>राष्ट्रकूट ( कन्नड़ : ರಾಷ್ಟ್ರಕೂಟ ) दक्षिण भारत, मध्य भारत और उत्तरी भारत के बड़े भूभाग पर राज्य (735-982) करने वाला राजवंश था।</t>
+  </si>
+  <si>
+    <t>https://hi.wikipedia.org/w/index.php?title=%E0%A4%B0%E0%A4%BE%E0%A4%B7%E0%A5%8D%E0%A4%9F%E0%A5%8D%E0%A4%B0%E0%A4%95%E0%A5%82%E0%A4%9F_%E0%A4%B0%E0%A4%BE%E0%A4%9C%E0%A4%B5%E0%A4%82%E0%A4%B6&amp;oldid=6582908</t>
+  </si>
+  <si>
+    <t>रेड्डी राजवंश</t>
+  </si>
+  <si>
+    <t>रेड्डी राजवंश के प्रोलया वेमा रेड्डी द्वारा दक्षिण भारत में रेड्डी साम्राज्य या कोंडाविडु रेड्डी साम्राज्य (1325-1448 सीई) स्थापित किया था। काकतीय राजवंश के शिलालेख और वंशावली से पता चलता है कि वे गत काकतीय 'सैन्य' से पैदा हुए थे, और स्थानीय तेलुगु योद्धा संस्कृति के साथ जुडे हुए थे।</t>
+  </si>
+  <si>
+    <t>https://hi.wikipedia.org/w/index.php?title=%E0%A4%B0%E0%A5%87%E0%A4%A1%E0%A5%8D%E0%A4%A1%E0%A5%80_%E0%A4%B0%E0%A4%BE%E0%A4%9C%E0%A4%B5%E0%A4%82%E0%A4%B6&amp;oldid=6630060</t>
+  </si>
+  <si>
+    <t>लोहारा राजवंश</t>
+  </si>
+  <si>
+    <t>लोहार वंश भारतीय उपमहाद्वीप के उत्तरी भाग में 1003 और लगभग 1320 सीई के बीच कश्मीर के हिंदू शासक थे। राजवंश के प्रारंभिक इतिहास का वर्णन राजतरंगिणी ( राजाओं का क्रॉनिकल ) में किया गया है, जो 12 वीं शताब्दी के मध्य में कल्हण द्वारा लिखी गई एक रचना है और जिस पर राजवंश के पहले 150 वर्षों के कई और शायद सभी अध्ययन निर्भर करते हैं। बाद के खाते, जो राजवंश के अंत तक और उसके बाद की जानकारी प्रदान करते हैं, जोनाराज और श्रीवर से आते हैं। राजवंश के बाद के शासक कमजोर थे: इस अवधि के दौरान आंतरिक लड़ाई और भ्रष्टाचार स्थानिक था, केवल कुछ वर्षों की राहत के साथ, इस क्षेत्र में इस्लामी हमलों के विकास के लिए वंश को कमजोर बना दिया।</t>
+  </si>
+  <si>
+    <t>https://hi.wikipedia.org/w/index.php?title=%E0%A4%B2%E0%A5%8B%E0%A4%B9%E0%A4%BE%E0%A4%B0%E0%A4%BE_%E0%A4%B0%E0%A4%BE%E0%A4%9C%E0%A4%B5%E0%A4%82%E0%A4%B6&amp;oldid=6629868</t>
+  </si>
+  <si>
+    <t>काकतीय वंश</t>
+  </si>
+  <si>
+    <t>११९० ई. के बाद जब कल्याण के चालुक्यों का साम्राज्य टूटकर बिखर गया तब उसके एक भाग के स्वामी वारंगल के काकतीय हुए; दूसरे के द्वारसमुद्र के होएसल और तीसरे के देवगिरि के यादव हुए। स्वाभाविक ही यह भूमि काकतीयों के अन्य शक्तियों से संघर्ष का कारण बन गई। काकतीयों की शक्ति प्रोलराज द्वितीय के समय विशेष बढ़ी। उसके पौत्र गणपति ने दक्षिण में कांची तक अपने साम्राज्य का विस्तार किया। गणपति की कन्या रुद्रंमा इतिहास में प्रसिद्ध हो गई है। उसकी शासननीति के प्रभाव से काकतीय साम्राज्य की समुन्नति हुई। वेनिस के यात्री मार्को पोलो ने रुद्रंमा की बड़ी सराहना की है।।</t>
+  </si>
+  <si>
+    <t>https://hi.wikipedia.org/w/index.php?title=%E0%A4%95%E0%A4%BE%E0%A4%95%E0%A4%A4%E0%A5%80%E0%A4%AF_%E0%A4%B5%E0%A4%82%E0%A4%B6&amp;oldid=6620011</t>
+  </si>
+  <si>
+    <t>विष्णुकुण्डिन राजवंश</t>
+  </si>
+  <si>
+    <t>विष्णुकुंडिन राजवंश ( आईएएसटी : Viṣṇukuṇḍina, कभी-कभी Viṣukuṇḍin), एक भारतीय राजवंश था जिसने 5वीं से 7वीं शताब्दी के बीच वर्तमान आंध्र प्रदेश , तेलंगाना , महाराष्ट्र , ओडिशा और दक्षिण भारत के अन्य हिस्सों पर शासन किया। वे माधव वर्मा के शासनकाल के दौरान एक स्वतंत्र शक्ति के रूप में उभरे, जिन्होंने शालंकायनों से तटीय आंध्र को जीतकर एलुरु के पास देंदुलुरु में अपनी राजधानी स्थापित की। उनके शासन ने दक्कन क्षेत्र के इतिहास को महत्वपूर्ण रूप से आकार दिया। हालाँकि, चालुक्य राजा पुलकेशिन द्वितीय द्वारा पूर्वी दक्कन को जीतने के साथ उनका शासन समाप्त हो गया, जिसने अपने भाई कुब्ज विष्णुवर्धन को वायसराय नियुक्त किया। विष्णुवर्धन ने बाद में स्वतंत्रता की घोषणा करते हुए पूर्वी चालुक्य वंश की स्थापना की।</t>
+  </si>
+  <si>
+    <t>https://hi.wikipedia.org/w/index.php?title=%E0%A4%B5%E0%A4%BF%E0%A4%B7%E0%A5%8D%E0%A4%A3%E0%A5%81%E0%A4%95%E0%A5%81%E0%A4%A3%E0%A5%8D%E0%A4%A1%E0%A4%BF%E0%A4%A8_%E0%A4%B0%E0%A4%BE%E0%A4%9C%E0%A4%B5%E0%A4%82%E0%A4%B6&amp;oldid=6425108</t>
+  </si>
+  <si>
+    <t>शालंकायन राजवंश</t>
+  </si>
+  <si>
+    <t>प्राचीन भारत के शालंकायन राजवंश ने 300 ई० से 440 ईस्वी तक भारत में आंध्र क्षेत्र के एक भाग पर शासन किया। उनका राज्य गोदावरी और कृष्ण नदियों के बीच स्थित था। उनकी राजधानी वेंगी थी जो वर्तमान में आंध्र प्रदेश के पश्चिम गोदावरी जिले में एलुरु के पास पेडावेगी में स्थित थी।</t>
+  </si>
+  <si>
+    <t>https://hi.wikipedia.org/w/index.php?title=%E0%A4%B6%E0%A4%BE%E0%A4%B2%E0%A4%82%E0%A4%95%E0%A4%BE%E0%A4%AF%E0%A4%A8_%E0%A4%B0%E0%A4%BE%E0%A4%9C%E0%A4%B5%E0%A4%82%E0%A4%B6&amp;oldid=6389980</t>
+  </si>
+  <si>
+    <t>शिलाहार राजवंश</t>
+  </si>
+  <si>
+    <t>शिलाहार राजवंश , राष्ट्रकूट काल के दौरान उत्तरी और दक्षिणी कोंकण (वर्तमान मुंबई और दक्षिणी महाराष्ट्र) में स्थापित एक शाही राजवंश था। यह राजवंश तीन शाखाओं में विभाजित था - एक शाखा ने उत्तरी कोंकण पर शासन किया, दूसरी शाखा ने दक्षिणी कोंकण पर शासन किया, और तीसरी शाखा ने 940 और 1215 के बीच कोल्हापुर , सतारा और बेलगाम के आधुनिक जिले पर शासन किया। इसके बाद इनपर चालुक्य वंश ने अधिकार कर लिया।</t>
+  </si>
+  <si>
+    <t>https://hi.wikipedia.org/w/index.php?title=%E0%A4%B6%E0%A4%BF%E0%A4%B2%E0%A4%BE%E0%A4%B9%E0%A4%BE%E0%A4%B0_%E0%A4%B0%E0%A4%BE%E0%A4%9C%E0%A4%B5%E0%A4%82%E0%A4%B6&amp;oldid=5798853</t>
+  </si>
+  <si>
+    <t>शैलोद्भव वंश</t>
+  </si>
+  <si>
+    <t>शैलोद्भव राजवंश ने ६ठी से ८वीं शताब्दी के मध्य भारत पूर्वी भागों पर शासन किया। उनके राज्य का मुख्य भाग कोंगोद-मण्डल कहलाता था जिसके अन्तर्गत वर्तमना समय के ओड़ीसा के गंजाम जिला , खोर्धा जिला और पुरी जिले आते हैं। उनकी राजधानी कोंगोद थी जो वर्तमान समय की बाणपुर है।</t>
+  </si>
+  <si>
+    <t>https://hi.wikipedia.org/w/index.php?title=%E0%A4%B6%E0%A5%88%E0%A4%B2%E0%A5%8B%E0%A4%A6%E0%A5%8D%E0%A4%AD%E0%A4%B5_%E0%A4%B5%E0%A4%82%E0%A4%B6&amp;oldid=5559700</t>
+  </si>
+  <si>
+    <t>संगम राजवंश</t>
+  </si>
+  <si>
+    <t>यह विजयनगर साम्राज्य का राजवंश जो कि हरिहर और बुक्का द्वारा स्थापित था।</t>
+  </si>
+  <si>
+    <t>https://hi.wikipedia.org/w/index.php?title=%E0%A4%B8%E0%A4%82%E0%A4%97%E0%A4%AE_%E0%A4%B0%E0%A4%BE%E0%A4%9C%E0%A4%B5%E0%A4%82%E0%A4%B6&amp;oldid=6230642</t>
+  </si>
+  <si>
+    <t>सम्माँ राजवंश</t>
+  </si>
+  <si>
+    <t>सम्माँ राजवंश ( सिन्धी : ur , सम्मन जो राज ) या सम्मा राजवंश ( अंग्रेज़ी : Samma Dynasty ) 1335 ईसवी से 1520 ईसवी काल में सिंध तथा बलोचिस्तान व पंजाब के कुछ हिस्सों में राज किया था। उनकी राजधानी ठठ्ठा शहर था। इस वंश की स्थापना जाम उनड़​ ( ur , Jam Unar ) ने की थी। उन्होंने सिंध में कुछ महान पुरातन-स्थल छोड़े हैं जिनमें ठठ्ठा का शाही समाधि-क्षेत्र शामिल है। इस राजवंश के बाद सिंध में अरग़ून​ राजवंश का क़ब्ज़ा हो गया। ।samma rajput are belongs to yaduvanshi line age of chandravansh, jadeja jadun bhatti chudasamma are also decedents hindu samma rajputra. Samma name came from one of descendent of krishna whose name is samnat ji</t>
+  </si>
+  <si>
+    <t>https://hi.wikipedia.org/w/index.php?title=%E0%A4%B8%E0%A4%AE%E0%A5%8D%E0%A4%AE%E0%A4%BE%E0%A4%81_%E0%A4%B0%E0%A4%BE%E0%A4%9C%E0%A4%B5%E0%A4%82%E0%A4%B6&amp;oldid=6113845</t>
+  </si>
+  <si>
+    <t>सातवाहन</t>
+  </si>
+  <si>
+    <t>सातवाहन राजवंश या सातवाहन साम्राज्य , जिसे प्राचीन भारतीय साहित्य में आंध्र राजवंश और आंध्र-सातवाहन राजवंश भी कहा गया हैं। यह प्राचीन भारत का हिंदू राजवंश था। सातवाहन राजाओं ने 150 वर्षों तक शासन किया। सातवाहन वंश की स्थापना 230 से 60 ईसा पूर्व के बीच राजा ने की थी। सातवाहन राजवंंश के सीमुक , शातकर्णी प्रथम , गौतमी पुत्र शातकर्णी , वासिष्ठीपुत्र पुलुमावी , शातकारणी प्रमुख राजा थे। पैठण और भोकरदन सातवाहन वंश की राजधानी रही , यह महाराष्ट्र के छत्रपति संभाजीनगर जिले में है। सातवाहन साम्राज्य की राजकीय भाषा [पाली]] और मराठी प्राकृत थी। इस समय अमरावती कला का विकास हुआ था। सातवाहन राजवंश के समय "समाज मातृसत्तात्म " था, अर्थात राजाओं के नाम उनकी माता के नाम पर (जैसे, गौतमीपुत्र शातकारणी ) रखने की प्रथा थी, लेकिन सातवाहन राजकुल मातृसत्तात्मक था, क्योंकि राजसिंहासन का उत्तराधिकारी वंशानुगत ही होता था।</t>
+  </si>
+  <si>
+    <t>https://hi.wikipedia.org/w/index.php?title=%E0%A4%B8%E0%A4%BE%E0%A4%A4%E0%A4%B5%E0%A4%BE%E0%A4%B9%E0%A4%A8&amp;oldid=6570296</t>
+  </si>
+  <si>
+    <t>सोमवंशी राजवंश</t>
+  </si>
+  <si>
+    <t>सोमवंशी राजवंश या केशरी वंश ने 9वीं से 12वीं शताब्दी के बीच पूर्वी भारत में वर्तमान ओडिशा के कुछ भागों पर शासन किया था । उनकी राजधानी पहले ययातिनगर (आधुनिक बिनिका ) और फिर अभिनव-ययातिनगर (आधुनिक जाजपुर ) थीं।</t>
+  </si>
+  <si>
+    <t>https://hi.wikipedia.org/w/index.php?title=%E0%A4%B8%E0%A5%8B%E0%A4%AE%E0%A4%B5%E0%A4%82%E0%A4%B6%E0%A5%80_%E0%A4%B0%E0%A4%BE%E0%A4%9C%E0%A4%B5%E0%A4%82%E0%A4%B6&amp;oldid=6616293</t>
+  </si>
+  <si>
+    <t>होयसल राजवंश</t>
+  </si>
+  <si>
+    <t>होयसल प्राचीन दक्षिण भारत का एक यादव राजवंश था। यह देवगिरी के यादव राजवंश की एक शाखा थी। होयसल राजाओ के शिलालेखों में भी उनको 'यदुकुलतिलक' कहा गया है। इस राजवंश ने १०वीं से १४वीं शताब्दी तक राज किया। उन्होने वर्तमान कर्नाटक के लगभग सम्पूर्ण भाग तथा तमिलनाडु के कावेरी नदी की उपजाऊ घाटी वाले भाग पर अपना अधिकार जमा लिया। इन्होंने ३१७ वर्ष राज किया। इनकी राजधानी पहले बेलूर थी पर बाद में स्थानांतरित होकर हालेबिदु हो गई।</t>
+  </si>
+  <si>
+    <t>https://hi.wikipedia.org/w/index.php?title=%E0%A4%B9%E0%A5%8B%E0%A4%AF%E0%A4%B8%E0%A4%B2_%E0%A4%B0%E0%A4%BE%E0%A4%9C%E0%A4%B5%E0%A4%82%E0%A4%B6&amp;oldid=6615844</t>
   </si>
 </sst>
 </file>
@@ -286,10 +739,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -630,18 +1086,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F15"/>
+  <dimension ref="A1:C76"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="1" width="12" customWidth="1"/>
-    <col min="2" max="2" width="16" customWidth="1"/>
-    <col min="3" max="3" width="27" customWidth="1"/>
-    <col min="4" max="4" width="28" customWidth="1"/>
-    <col min="5" max="5" width="12" customWidth="1"/>
-    <col min="6" max="6" width="13" customWidth="1"/>
+    <col min="1" max="1" width="36" customWidth="1"/>
+    <col min="2" max="2" width="110" customWidth="1"/>
+    <col min="3" max="3" width="90" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -651,298 +1104,834 @@
       <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+    </row>
+    <row r="2" ht="64" customHeight="1" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="B2" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="C2" s="2" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
+    <row r="3" ht="64" customHeight="1" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B3" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C3" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="D2" t="s">
+    </row>
+    <row r="4" ht="96" customHeight="1" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="E2" t="s">
+      <c r="B4" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="F2" t="s">
+      <c r="C4" s="2" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
+    <row r="5" ht="42" customHeight="1" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B5" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="C3" t="s">
+      <c r="C5" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="D3" t="s">
+    </row>
+    <row r="6" ht="80" customHeight="1" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="E3" t="s">
+      <c r="B6" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="F3" t="s">
+      <c r="C6" s="2" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
+    <row r="7" ht="42" customHeight="1" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B7" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="C4" t="s">
+      <c r="C7" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="D4" t="s">
+    </row>
+    <row r="8" ht="42" customHeight="1" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="E4" t="s">
-        <v>16</v>
-      </c>
-      <c r="F4" t="s">
+      <c r="B8" s="2" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
+      <c r="C8" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="B5" t="s">
+    </row>
+    <row r="9" ht="288" customHeight="1" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="C5" t="s">
+      <c r="B9" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="D5" t="s">
+      <c r="C9" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="E5" t="s">
-        <v>16</v>
-      </c>
-      <c r="F5" t="s">
+    </row>
+    <row r="10" ht="42" customHeight="1" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="2" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
+      <c r="B10" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="B6" t="s">
+      <c r="C10" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="C6" t="s">
+    </row>
+    <row r="11" ht="64" customHeight="1" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="D6" t="s">
+      <c r="B11" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="E6" t="s">
-        <v>16</v>
-      </c>
-      <c r="F6" t="s">
+      <c r="C11" s="2" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
+    <row r="12" ht="48" customHeight="1" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B12" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="C7" t="s">
+      <c r="C12" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="D7" t="s">
+    </row>
+    <row r="13" ht="48" customHeight="1" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="E7" t="s">
-        <v>16</v>
-      </c>
-      <c r="F7" t="s">
+      <c r="B13" s="2" t="s">
         <v>37</v>
       </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
+      <c r="C13" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="B8" t="s">
+    </row>
+    <row r="14" ht="96" customHeight="1" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="C8" t="s">
+      <c r="B14" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="D8" t="s">
+      <c r="C14" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="E8" t="s">
-        <v>16</v>
-      </c>
-      <c r="F8" t="s">
+    </row>
+    <row r="15" ht="64" customHeight="1" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="2" t="s">
         <v>42</v>
       </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
+      <c r="B15" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="B9" t="s">
+      <c r="C15" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="C9" t="s">
+    </row>
+    <row r="16" ht="80" customHeight="1" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="D9" t="s">
-        <v>21</v>
-      </c>
-      <c r="E9" t="s">
-        <v>16</v>
-      </c>
-      <c r="F9" t="s">
+      <c r="B16" s="2" t="s">
         <v>46</v>
       </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
+      <c r="C16" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="B10" t="s">
+    </row>
+    <row r="17" ht="80" customHeight="1" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="C10" t="s">
+      <c r="B17" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="D10" t="s">
+      <c r="C17" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="E10" t="s">
+    </row>
+    <row r="18" ht="42" customHeight="1" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="F10" t="s">
+      <c r="B18" s="2" t="s">
         <v>52</v>
       </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
+      <c r="C18" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="B11" t="s">
+    </row>
+    <row r="19" ht="64" customHeight="1" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="C11" t="s">
+      <c r="B19" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="D11" t="s">
+      <c r="C19" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="E11" t="s">
-        <v>10</v>
-      </c>
-      <c r="F11" t="s">
+    </row>
+    <row r="20" ht="80" customHeight="1" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="2" t="s">
         <v>57</v>
       </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
+      <c r="B20" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="B12" t="s">
+      <c r="C20" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="C12" t="s">
+    </row>
+    <row r="21" ht="42" customHeight="1" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="D12" t="s">
+      <c r="B21" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="E12" t="s">
-        <v>16</v>
-      </c>
-      <c r="F12" t="s">
+      <c r="C21" s="2" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
+    <row r="22" ht="112" customHeight="1" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="B13" t="s">
+      <c r="B22" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="C13" t="s">
+      <c r="C22" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="D13" t="s">
+    </row>
+    <row r="23" ht="64" customHeight="1" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="E13" t="s">
-        <v>10</v>
-      </c>
-      <c r="F13" t="s">
+      <c r="B23" s="2" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
+      <c r="C23" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="B14" t="s">
+    </row>
+    <row r="24" ht="42" customHeight="1" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="C14" t="s">
+      <c r="B24" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="D14" t="s">
-        <v>21</v>
-      </c>
-      <c r="E14" t="s">
-        <v>16</v>
-      </c>
-      <c r="F14" t="s">
+      <c r="C24" s="2" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
+    <row r="25" ht="48" customHeight="1" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="B15" t="s">
+      <c r="B25" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="C15" t="s">
+      <c r="C25" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="D15" t="s">
+    </row>
+    <row r="26" ht="48" customHeight="1" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="E15" t="s">
-        <v>16</v>
-      </c>
-      <c r="F15" t="s">
+      <c r="B26" s="2" t="s">
         <v>76</v>
       </c>
+      <c r="C26" s="2" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="27" ht="48" customHeight="1" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="28" ht="64" customHeight="1" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="29" ht="48" customHeight="1" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="30" ht="48" customHeight="1" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="31" ht="64" customHeight="1" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="B31" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="32" ht="64" customHeight="1" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="B32" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="33" ht="64" customHeight="1" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="B33" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="C33" s="2" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="34" ht="42" customHeight="1" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="B34" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="35" ht="42" customHeight="1" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="B35" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="36" ht="128" customHeight="1" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="B36" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="C36" s="2" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="37" ht="48" customHeight="1" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="B37" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="C37" s="2" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="38" ht="64" customHeight="1" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="B38" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="C38" s="2" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="39" ht="192" customHeight="1" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A39" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="B39" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="C39" s="2" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="40" ht="64" customHeight="1" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A40" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="B40" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="C40" s="2" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="41" ht="128" customHeight="1" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A41" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="B41" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="C41" s="2" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="42" ht="192" customHeight="1" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A42" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="B42" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="C42" s="2" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="43" ht="48" customHeight="1" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A43" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="B43" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="C43" s="2" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="44" ht="64" customHeight="1" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A44" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="B44" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="C44" s="2" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="45" ht="48" customHeight="1" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A45" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="B45" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="C45" s="2" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="46" ht="64" customHeight="1" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A46" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="B46" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="C46" s="2" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="47" ht="42" customHeight="1" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A47" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="B47" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="C47" s="2" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="48" ht="96" customHeight="1" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A48" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="B48" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="C48" s="2" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="49" ht="48" customHeight="1" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A49" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="B49" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="C49" s="2" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="50" ht="144" customHeight="1" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A50" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="B50" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="C50" s="2" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="51" ht="160" customHeight="1" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A51" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="B51" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="C51" s="2" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="52" ht="96" customHeight="1" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A52" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="B52" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="C52" s="2" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="53" ht="42" customHeight="1" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A53" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="B53" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="C53" s="2" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="54" ht="144" customHeight="1" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A54" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="B54" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="C54" s="2" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="55" ht="48" customHeight="1" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A55" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="B55" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="C55" s="2" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="56" ht="96" customHeight="1" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A56" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="B56" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="C56" s="2" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="57" ht="144" customHeight="1" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A57" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="B57" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="C57" s="2" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="58" ht="42" customHeight="1" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A58" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="B58" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="C58" s="2" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="59" ht="48" customHeight="1" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A59" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="B59" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="C59" s="2" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="60" ht="48" customHeight="1" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A60" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="B60" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="C60" s="2" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="61" ht="64" customHeight="1" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A61" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="B61" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="C61" s="2" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="62" ht="42" customHeight="1" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A62" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="B62" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="C62" s="2" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="63" ht="80" customHeight="1" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A63" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="B63" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="C63" s="2" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="64" ht="48" customHeight="1" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A64" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="B64" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="C64" s="2" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="65" ht="48" customHeight="1" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A65" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="B65" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="C65" s="2" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="66" ht="112" customHeight="1" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A66" s="2" t="s">
+        <v>195</v>
+      </c>
+      <c r="B66" s="2" t="s">
+        <v>196</v>
+      </c>
+      <c r="C66" s="2" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="67" ht="96" customHeight="1" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A67" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="B67" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="C67" s="2" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="68" ht="128" customHeight="1" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A68" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="B68" s="2" t="s">
+        <v>202</v>
+      </c>
+      <c r="C68" s="2" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="69" ht="48" customHeight="1" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A69" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="B69" s="2" t="s">
+        <v>205</v>
+      </c>
+      <c r="C69" s="2" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="70" ht="80" customHeight="1" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A70" s="2" t="s">
+        <v>207</v>
+      </c>
+      <c r="B70" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="C70" s="2" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="71" ht="48" customHeight="1" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A71" s="2" t="s">
+        <v>210</v>
+      </c>
+      <c r="B71" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="C71" s="2" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="72" ht="42" customHeight="1" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A72" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="B72" s="2" t="s">
+        <v>214</v>
+      </c>
+      <c r="C72" s="2" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="73" ht="112" customHeight="1" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A73" s="2" t="s">
+        <v>216</v>
+      </c>
+      <c r="B73" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="C73" s="2" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="74" ht="144" customHeight="1" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A74" s="2" t="s">
+        <v>219</v>
+      </c>
+      <c r="B74" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="C74" s="2" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="75" ht="48" customHeight="1" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A75" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="B75" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="C75" s="2" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="76" ht="80" customHeight="1" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A76" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="B76" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="C76" s="2" t="s">
+        <v>227</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F1"/>
+  <autoFilter ref="A1:C1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
